--- a/site/assets/project_bastion_model.xlsx
+++ b/site/assets/project_bastion_model.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11536</v>
+        <v>11723</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5531.5</v>
+        <v>5495.5</v>
       </c>
     </row>
     <row r="12">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>13722.2995968</v>
+        <v>13736.8600576</v>
       </c>
     </row>
     <row r="15">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2374.2500864</v>
+        <v>2369.1399168</v>
       </c>
     </row>
     <row r="16">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>6182.989824</v>
+        <v>6205.5698432</v>
       </c>
     </row>
     <row r="17">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>7036.4410041401</v>
+        <v>7037.252320775599</v>
       </c>
     </row>
     <row r="18">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>6361.22</v>
+        <v>6319.82</v>
       </c>
     </row>
     <row r="20">
@@ -852,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -864,6 +864,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -912,6 +913,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -938,10 +944,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>12.27</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v/>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -950,7 +956,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; 46.8% from promoters + open offer</t>
+          <t>VERIFIED — Ambuja to acquire 46.8% of Orient Cement (37.9% promoters + 8.9% public) at equity value Rs 8100 cr; open offer 26% at Rs 395.40/sh = 12.27% premium to Rs 352.2 prev close; announced 22 Oct 2024; EV/EBITDA unverified</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/markets/capital-market-news/ambuja-cements-to-46-8-stake-in-orient-cement-announces-open-offer-at-rs-395-40-share-124102200252_1.html</t>
         </is>
       </c>
     </row>
@@ -994,6 +1005,11 @@
           <t>ILLUSTRATIVE — verify; unlisted south-India capacity buy</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.bseindia.com/corporates/ann.html</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1012,7 +1028,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7600</v>
+        <v>5379</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1020,10 +1036,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v/>
+        <v>24.1</v>
       </c>
       <c r="G4" t="n">
-        <v>11</v>
+        <v/>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1032,7 +1048,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; demerger + share swap 1:52</t>
+          <t>VERIFIED — demerger of Kesoram cement (10.75 mtpa; Sedam + Basantnagar) into UltraTech; share swap 1 UltraTech per 52 Kesoram; implied offer Rs 173.15 = 24.1% premium to Rs 139.45 prev close; deal ~Rs 5379 cr; appointed date 1 Apr 2024; scheme effective 1 Mar 2025; EV/EBITDA unverified</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.businesstoday.in/latest/corporate/story/ultratech-cement-to-buy-kesorams-cement-business-in-rs-5379-cr-deal-announces-swap-ratio-of-152-407773-2023-11-30</t>
         </is>
       </c>
     </row>
@@ -1076,6 +1097,11 @@
           <t>ILLUSTRATIVE — verify; distressed cement consolidation; open offer</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.sebi.gov.in/filings/takeovers.html</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1105,16 +1131,21 @@
         <v/>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v/>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>announced</t>
+          <t>withdrawn</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; asset purchase; long-running closing</t>
+          <t>VERIFIED — Dec 2022 binding framework (EV Rs 5666 cr; 9.4 mtpa) fell through after JAL admitted to insolvency and JAL-UltraTech arbitration; superseded by fresh BTA 21 May 2026 with JAL (acquired by Adani under IBC) + Adani Infra at EV Rs 2850 cr for 5.2 mtpa Central region (Rewa/Churk/Chunar/Sadwa); EV/EBITDA unverified</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.businessupturn.com/business/dalmia-bharat-acquires-5-2-mntpa-cement-capacity-from-jal-for-rs-2850-crore</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1177,7 @@
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v/>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1155,7 +1186,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; Holcim India exit incl ACC; open offers for both</t>
+          <t>VERIFIED — Holcim India exit; Adani bought 63.19% Ambuja ~Rs 385/sh; open offer 26% at Rs 385 (~7% premium; ~Rs 19880 cr); part of USD 10.5 bn Ambuja+ACC deal; EV/EBITDA unverified</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.adani.com/newsroom/media-releases/adani-to-acquire-holcims-stake-in-ambuja-cements-and-acc-limited</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v/>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1196,7 +1232,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — verify; acquired via Ambuja/Holcim transaction</t>
+          <t>VERIFIED — acquired via Ambuja/Holcim (Holcim held 54.53% incl 50.05% via Ambuja); open offer 26% at Rs 2300 (~7% premium; ~Rs 11260 cr); part of USD 10.5 bn deal; EV/EBITDA unverified</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.adani.com/newsroom/media-releases/adani-to-acquire-holcims-stake-in-ambuja-cements-and-acc-limited</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1885,7 @@
         <v/>
       </c>
       <c r="F3" s="14">
-        <f>B3-178.80141848187375</f>
+        <f>B3-179.68943379284622</f>
         <v/>
       </c>
     </row>
@@ -1890,7 +1931,7 @@
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>B5--0.3558624992782163</f>
+        <f>B5--0.35266339734787855</f>
         <v/>
       </c>
     </row>
@@ -2037,7 +2078,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Acquiring 64% crosses the 25% threshold -&gt; mandatory open offer for 26% of the target at the floor price (modeled at the Rs 6,361 offer price; real floor is the highest-of tests incl. 60-day VWAP).</t>
+          <t>Acquiring 64% crosses the 25% threshold -&gt; mandatory open offer for 26% of the target at the floor price (modeled at the Rs 6,320 offer price; real floor is the highest-of tests incl. 60-day VWAP).</t>
         </is>
       </c>
     </row>
@@ -2051,14 +2092,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>50% acceptance: buy 1.00 Cr shares for Rs 6,390 Cr; post-offer holding 77.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
+          <t>50% acceptance: buy 1.00 Cr shares for Rs 6,348 Cr; post-offer holding 77.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100% acceptance: buy 2.01 Cr shares for Rs 12,780 Cr; post-offer holding 90.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
+          <t>100% acceptance: buy 2.01 Cr shares for Rs 12,696 Cr; post-offer holding 90.0%. BREACHES 75% MPS — must sell down within 12 months or pursue delisting (requires 90%).</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2113,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deal value Rs 31,457 Cr exceeds the Rs 2,000 Cr deal-value threshold (2024 amendment) — CCI approval required; expect ~150-210 days outer timeline, Green Channel possible if no overlaps.</t>
+          <t>Deal value Rs 31,253 Cr exceeds the Rs 2,000 Cr deal-value threshold (2024 amendment) — CCI approval required; expect ~150-210 days outer timeline, Green Channel possible if no overlaps.</t>
         </is>
       </c>
     </row>
@@ -2361,31 +2402,31 @@
         <v>5</v>
       </c>
       <c r="B4" s="18" t="n">
-        <v>-23.95</v>
+        <v>-23.74</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>-23.53</v>
+        <v>-23.32</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>-23.1</v>
+        <v>-22.9</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>-22.68</v>
+        <v>-22.47</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>-22.26</v>
+        <v>-22.05</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>-21.83</v>
+        <v>-21.62</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>-21.41</v>
+        <v>-21.2</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>-20.98</v>
+        <v>-20.78</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>-20.56</v>
+        <v>-20.35</v>
       </c>
     </row>
     <row r="5">
@@ -2393,31 +2434,31 @@
         <v>7.5</v>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-24.71</v>
+        <v>-24.5</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>-24.29</v>
+        <v>-24.07</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>-23.86</v>
+        <v>-23.65</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-23.44</v>
+        <v>-23.23</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>-23.01</v>
+        <v>-22.8</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>-22.59</v>
+        <v>-22.38</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>-22.17</v>
+        <v>-21.95</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>-21.74</v>
+        <v>-21.53</v>
       </c>
       <c r="J5" s="18" t="n">
-        <v>-21.32</v>
+        <v>-21.11</v>
       </c>
     </row>
     <row r="6">
@@ -2425,31 +2466,31 @@
         <v>10</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>-25.47</v>
+        <v>-25.25</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>-25.05</v>
+        <v>-24.83</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>-24.62</v>
+        <v>-24.4</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>-24.2</v>
+        <v>-23.98</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>-23.77</v>
+        <v>-23.56</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>-23.35</v>
+        <v>-23.13</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>-22.93</v>
+        <v>-22.71</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>-22.5</v>
+        <v>-22.29</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>-22.08</v>
+        <v>-21.86</v>
       </c>
     </row>
     <row r="7">
@@ -2457,31 +2498,31 @@
         <v>12.5</v>
       </c>
       <c r="B7" s="18" t="n">
-        <v>-26.23</v>
+        <v>-26.01</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>-25.8</v>
+        <v>-25.58</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>-25.38</v>
+        <v>-25.16</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-24.96</v>
+        <v>-24.73</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-24.53</v>
+        <v>-24.31</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-24.11</v>
+        <v>-23.89</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-23.69</v>
+        <v>-23.46</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-23.26</v>
+        <v>-23.04</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>-22.84</v>
+        <v>-22.62</v>
       </c>
     </row>
     <row r="8">
@@ -2489,31 +2530,31 @@
         <v>15</v>
       </c>
       <c r="B8" s="18" t="n">
-        <v>-26.99</v>
+        <v>-26.76</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>-26.56</v>
+        <v>-26.34</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-26.14</v>
+        <v>-25.91</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-25.72</v>
+        <v>-25.49</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-25.29</v>
+        <v>-25.07</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-24.87</v>
+        <v>-24.64</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-24.44</v>
+        <v>-24.22</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-24.02</v>
+        <v>-23.79</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-23.6</v>
+        <v>-23.37</v>
       </c>
     </row>
     <row r="9">
@@ -2521,31 +2562,31 @@
         <v>17.5</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>-27.75</v>
+        <v>-27.51</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>-27.32</v>
+        <v>-27.09</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>-26.9</v>
+        <v>-26.67</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-26.48</v>
+        <v>-26.24</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>-26.05</v>
+        <v>-25.82</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>-25.63</v>
+        <v>-25.4</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>-25.2</v>
+        <v>-24.97</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>-24.78</v>
+        <v>-24.55</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>-24.36</v>
+        <v>-24.12</v>
       </c>
     </row>
     <row r="10">
@@ -2553,31 +2594,31 @@
         <v>20</v>
       </c>
       <c r="B10" s="18" t="n">
-        <v>-28.51</v>
+        <v>-28.27</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>-28.08</v>
+        <v>-27.85</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>-27.66</v>
+        <v>-27.42</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-27.23</v>
+        <v>-27</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>-26.81</v>
+        <v>-26.57</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>-26.39</v>
+        <v>-26.15</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>-25.96</v>
+        <v>-25.73</v>
       </c>
       <c r="I10" s="18" t="n">
-        <v>-25.54</v>
+        <v>-25.3</v>
       </c>
       <c r="J10" s="18" t="n">
-        <v>-25.12</v>
+        <v>-24.88</v>
       </c>
     </row>
     <row r="11">
@@ -2585,31 +2626,31 @@
         <v>22.5</v>
       </c>
       <c r="B11" s="18" t="n">
-        <v>-29.27</v>
+        <v>-29.02</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>-28.84</v>
+        <v>-28.6</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>-28.42</v>
+        <v>-28.18</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-27.99</v>
+        <v>-27.75</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>-27.57</v>
+        <v>-27.33</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>-27.15</v>
+        <v>-26.9</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>-26.72</v>
+        <v>-26.48</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>-26.3</v>
+        <v>-26.06</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>-25.87</v>
+        <v>-25.63</v>
       </c>
     </row>
     <row r="12">
@@ -2617,31 +2658,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="18" t="n">
-        <v>-30.02</v>
+        <v>-29.78</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>-29.6</v>
+        <v>-29.35</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>-29.18</v>
+        <v>-28.93</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-28.75</v>
+        <v>-28.51</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-28.33</v>
+        <v>-28.08</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>-27.91</v>
+        <v>-27.66</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-27.48</v>
+        <v>-27.23</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>-27.06</v>
+        <v>-26.81</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>-26.63</v>
+        <v>-26.39</v>
       </c>
     </row>
     <row r="14">
@@ -2690,31 +2731,31 @@
         <v>0</v>
       </c>
       <c r="B16" s="18" t="n">
-        <v>-9.82</v>
+        <v>-9.59</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>-10.25</v>
+        <v>-10.01</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-10.67</v>
+        <v>-10.43</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>-11.09</v>
+        <v>-10.85</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>-11.51</v>
+        <v>-11.27</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>-11.93</v>
+        <v>-11.68</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>-12.35</v>
+        <v>-12.1</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>-12.77</v>
+        <v>-12.51</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>-13.18</v>
+        <v>-12.92</v>
       </c>
     </row>
     <row r="17">
@@ -2722,31 +2763,31 @@
         <v>10</v>
       </c>
       <c r="B17" s="18" t="n">
-        <v>-10.97</v>
+        <v>-10.75</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>-11.43</v>
+        <v>-11.2</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>-11.88</v>
+        <v>-11.65</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>-12.34</v>
+        <v>-12.1</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>-12.79</v>
+        <v>-12.54</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>-13.23</v>
+        <v>-12.99</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>-13.68</v>
+        <v>-13.43</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>-14.13</v>
+        <v>-13.87</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>-14.57</v>
+        <v>-14.32</v>
       </c>
     </row>
     <row r="18">
@@ -2754,31 +2795,31 @@
         <v>20</v>
       </c>
       <c r="B18" s="18" t="n">
-        <v>-12.15</v>
+        <v>-11.93</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>-12.63</v>
+        <v>-12.41</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>-13.12</v>
+        <v>-12.89</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>-13.6</v>
+        <v>-13.36</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>-14.08</v>
+        <v>-13.84</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>-14.56</v>
+        <v>-14.32</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>-15.04</v>
+        <v>-14.79</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>-15.51</v>
+        <v>-15.26</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>-15.99</v>
+        <v>-15.73</v>
       </c>
     </row>
     <row r="19">
@@ -2786,31 +2827,31 @@
         <v>30</v>
       </c>
       <c r="B19" s="18" t="n">
-        <v>-13.34</v>
+        <v>-13.12</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>-13.86</v>
+        <v>-13.63</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>-14.37</v>
+        <v>-14.14</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>-14.88</v>
+        <v>-14.65</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>-15.4</v>
+        <v>-15.16</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>-15.91</v>
+        <v>-15.67</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>-16.41</v>
+        <v>-16.17</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>-16.92</v>
+        <v>-16.67</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>-17.43</v>
+        <v>-17.18</v>
       </c>
     </row>
     <row r="20">
@@ -2818,31 +2859,31 @@
         <v>40</v>
       </c>
       <c r="B20" s="18" t="n">
-        <v>-14.55</v>
+        <v>-14.34</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>-15.1</v>
+        <v>-14.88</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>-15.65</v>
+        <v>-15.42</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>-16.19</v>
+        <v>-15.96</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-16.74</v>
+        <v>-16.5</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>-17.28</v>
+        <v>-17.04</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-17.82</v>
+        <v>-17.58</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-18.36</v>
+        <v>-18.11</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>-18.9</v>
+        <v>-18.65</v>
       </c>
     </row>
     <row r="21">
@@ -2850,31 +2891,31 @@
         <v>50</v>
       </c>
       <c r="B21" s="18" t="n">
-        <v>-15.78</v>
+        <v>-15.57</v>
       </c>
       <c r="C21" s="18" t="n">
-        <v>-16.36</v>
+        <v>-16.15</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>-16.94</v>
+        <v>-16.72</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>-17.52</v>
+        <v>-17.3</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>-18.1</v>
+        <v>-17.87</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>-18.67</v>
+        <v>-18.44</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>-19.25</v>
+        <v>-19.01</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>-19.82</v>
+        <v>-19.58</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>-20.39</v>
+        <v>-20.15</v>
       </c>
     </row>
     <row r="22">
@@ -2882,31 +2923,31 @@
         <v>60</v>
       </c>
       <c r="B22" s="18" t="n">
-        <v>-17.04</v>
+        <v>-16.83</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>-17.65</v>
+        <v>-17.43</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>-18.26</v>
+        <v>-18.04</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>-18.87</v>
+        <v>-18.65</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>-19.49</v>
+        <v>-19.26</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>-20.1</v>
+        <v>-19.86</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>-20.7</v>
+        <v>-20.47</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>-21.31</v>
+        <v>-21.07</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>-21.92</v>
+        <v>-21.67</v>
       </c>
     </row>
     <row r="23">
@@ -2914,31 +2955,31 @@
         <v>70</v>
       </c>
       <c r="B23" s="18" t="n">
-        <v>-18.31</v>
+        <v>-18.1</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>-18.96</v>
+        <v>-18.74</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>-19.61</v>
+        <v>-19.39</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>-20.25</v>
+        <v>-20.03</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>-20.9</v>
+        <v>-20.67</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>-21.54</v>
+        <v>-21.31</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>-22.19</v>
+        <v>-21.95</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>-22.83</v>
+        <v>-22.59</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>-23.47</v>
+        <v>-23.23</v>
       </c>
     </row>
     <row r="24">
@@ -2946,31 +2987,31 @@
         <v>80</v>
       </c>
       <c r="B24" s="18" t="n">
-        <v>-19.6</v>
+        <v>-19.39</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>-20.29</v>
+        <v>-20.07</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>-20.97</v>
+        <v>-20.75</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-21.65</v>
+        <v>-21.43</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-22.34</v>
+        <v>-22.11</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>-23.02</v>
+        <v>-22.79</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-23.7</v>
+        <v>-23.46</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-24.38</v>
+        <v>-24.14</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-25.06</v>
+        <v>-24.82</v>
       </c>
     </row>
     <row r="25">
@@ -2978,31 +3019,31 @@
         <v>90</v>
       </c>
       <c r="B25" s="18" t="n">
-        <v>-20.92</v>
+        <v>-20.71</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>-21.64</v>
+        <v>-21.43</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-22.36</v>
+        <v>-22.14</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-23.08</v>
+        <v>-22.86</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-23.8</v>
+        <v>-23.57</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-24.52</v>
+        <v>-24.29</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-25.24</v>
+        <v>-25</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-25.96</v>
+        <v>-25.72</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-26.68</v>
+        <v>-26.43</v>
       </c>
     </row>
     <row r="26">
@@ -3010,31 +3051,31 @@
         <v>100</v>
       </c>
       <c r="B26" s="18" t="n">
-        <v>-22.26</v>
+        <v>-22.05</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>-23.01</v>
+        <v>-22.8</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-23.77</v>
+        <v>-23.56</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-24.53</v>
+        <v>-24.31</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-25.29</v>
+        <v>-25.07</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-26.05</v>
+        <v>-25.82</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-26.81</v>
+        <v>-26.57</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-27.57</v>
+        <v>-27.33</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-28.33</v>
+        <v>-28.08</v>
       </c>
     </row>
   </sheetData>
